--- a/fabrication/boards/bms_afe_tester-1_0/bom-bms_afe_tester-1_0.xlsx
+++ b/fabrication/boards/bms_afe_tester-1_0/bom-bms_afe_tester-1_0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\zbrozek-git\solarcar-batterypack\bms\bms_afe_tester-1_0\outputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\zbrozek-git\solarcar-batterypack\fabrication\boards\bms_afe_tester-1_0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB4027FB-080C-4393-AD62-BB8BF1164D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7537B734-7470-4B42-8F4D-D6FBDD2380AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5180" yWindow="1800" windowWidth="28200" windowHeight="18290" xr2:uid="{7A91F977-5629-4F6F-AE6A-607BD59F2E3E}"/>
+    <workbookView xWindow="190" yWindow="470" windowWidth="28200" windowHeight="18290" xr2:uid="{7A91F977-5629-4F6F-AE6A-607BD59F2E3E}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials-bms_afe_teste" sheetId="1" r:id="rId1"/>
@@ -210,556 +210,556 @@
     <t>C47971</t>
   </si>
   <si>
+    <t>D2, D4A, D4B, D4C, D4D, D4E, D4F, D4G, D4H, D4I, D4J, D4K, D4L, D4M, D4N, D4O, D4P, D7A, D7B, D7C, D7D, D7E, D7F, D7G, D7H, D7I, D7J, D7K, D7L, D7M, D7N, D7O, D7P</t>
+  </si>
+  <si>
+    <t>B340A-13-F</t>
+  </si>
+  <si>
+    <t>C85098</t>
+  </si>
+  <si>
+    <t>SMA</t>
+  </si>
+  <si>
+    <t>D3A, D3B, D3C, D3D, D3E, D3F, D3G, D3H, D3I, D3J, D3K, D3L, D3M, D3N, D3O, D3P</t>
+  </si>
+  <si>
+    <t>PMEG10010ELR-QX</t>
+  </si>
+  <si>
+    <t>C5361358</t>
+  </si>
+  <si>
+    <t>SOD123W</t>
+  </si>
+  <si>
+    <t>D6</t>
+  </si>
+  <si>
+    <t>LTST-C190YKT</t>
+  </si>
+  <si>
+    <t>C125097</t>
+  </si>
+  <si>
+    <t>LED_0603P_YELLOW</t>
+  </si>
+  <si>
+    <t>D9</t>
+  </si>
+  <si>
+    <t>MM3Z15VC</t>
+  </si>
+  <si>
+    <t>C891582</t>
+  </si>
+  <si>
+    <t>SOD323</t>
+  </si>
+  <si>
+    <t>D17A, D17B</t>
+  </si>
+  <si>
+    <t>PESD2USB3UX</t>
+  </si>
+  <si>
+    <t>C3708426</t>
+  </si>
+  <si>
+    <t>3SOT23</t>
+  </si>
+  <si>
+    <t>FB1, FB3</t>
+  </si>
+  <si>
+    <t>BLM15PX601SN1D</t>
+  </si>
+  <si>
+    <t>C160977</t>
+  </si>
+  <si>
+    <t>FB0402</t>
+  </si>
+  <si>
+    <t>FB2</t>
+  </si>
+  <si>
+    <t>MPZ2012S102AT000</t>
+  </si>
+  <si>
+    <t>C76817</t>
+  </si>
+  <si>
+    <t>FB0805</t>
+  </si>
+  <si>
+    <t>H1, H2, H3, H4, H5, H6, H7, H8, H9, H10, H11, H12, H13, H14, H15, H16, H17, H18, H19, H20, H21, H22, H23, H24, H25, H26, H27, H28, H29, H30, H31, H32</t>
+  </si>
+  <si>
+    <t>SMTSO-M2-10ET</t>
+  </si>
+  <si>
+    <t>C2928171</t>
+  </si>
+  <si>
+    <t>J1</t>
+  </si>
+  <si>
+    <t>FTSH-107-01-L-DV-K-A</t>
+  </si>
+  <si>
+    <t>C5563894</t>
+  </si>
+  <si>
+    <t>SAMTEC_FTSH-107-01-L-DV-K-A</t>
+  </si>
+  <si>
+    <t>J2</t>
+  </si>
+  <si>
+    <t>0826-1L1T-57-F</t>
+  </si>
+  <si>
+    <t>C3179913</t>
+  </si>
+  <si>
+    <t>BELFUSE_0826-1L1T-57-F</t>
+  </si>
+  <si>
+    <t>J11A, J11B</t>
+  </si>
+  <si>
+    <t>TYPE-C-31-M-12</t>
+  </si>
+  <si>
+    <t>C165948</t>
+  </si>
+  <si>
+    <t>CONN_USBC_TYPE-C-31-M-12</t>
+  </si>
+  <si>
+    <t>L1, L2, L3</t>
+  </si>
+  <si>
+    <t>FTC404020S4R7MGCA</t>
+  </si>
+  <si>
+    <t>C39676072</t>
+  </si>
+  <si>
+    <t>SMD-4.1x4.1x2.0</t>
+  </si>
+  <si>
+    <t>Q1A, Q1B, Q1C, Q1D, Q1E, Q1F, Q1G, Q1H, Q1I, Q1J, Q1K, Q1L, Q1M, Q1N, Q1O, Q1P</t>
+  </si>
+  <si>
+    <t>IRLML0060TRPBF</t>
+  </si>
+  <si>
+    <t>C67274</t>
+  </si>
+  <si>
+    <t>Q3</t>
+  </si>
+  <si>
+    <t>DMP6023LFGQ-13</t>
+  </si>
+  <si>
+    <t>C672173</t>
+  </si>
+  <si>
+    <t>DIODES_POWERDI3333-8</t>
+  </si>
+  <si>
+    <t>R1, R2, R7, R24, R39, R60, R96, R97</t>
+  </si>
+  <si>
+    <t>0402WGF1001TCE</t>
+  </si>
+  <si>
+    <t>C11702</t>
+  </si>
+  <si>
+    <t>R0402</t>
+  </si>
+  <si>
+    <t>R3, R4, R5, R6, R22, R26, R32, R35, R36, R38, R40, R41, R69A, R69B, R69C, R69D, R81, R82, R91, R92, R93, R128A, R128B, R129A, R129B</t>
+  </si>
+  <si>
+    <t>CRCW040233R0FKED</t>
+  </si>
+  <si>
+    <t>C242490</t>
+  </si>
+  <si>
+    <t>R8A, R8B, R8C, R8D, R8E, R8F, R8G, R8H, R8I, R8J, R8K, R8L, R8M, R8N, R8O, R8P, R14A, R14B, R14C, R14D, R14E, R14F, R14G, R14H, R14I, R14J, R14K, R14L, R14M, R14N, R14O, R14P</t>
+  </si>
+  <si>
+    <t>CRCW06034R70FKEAHP</t>
+  </si>
+  <si>
+    <t>C313771</t>
+  </si>
+  <si>
+    <t>R0603</t>
+  </si>
+  <si>
+    <t>R9, R78</t>
+  </si>
+  <si>
+    <t>0402WGF9103TCE</t>
+  </si>
+  <si>
+    <t>C25800</t>
+  </si>
+  <si>
+    <t>R10A, R10B, R10C, R10D, R10E, R10F, R10G, R10H, R10I, R10J, R10K, R10L, R10M, R10N, R10O, R10P</t>
+  </si>
+  <si>
+    <t>ESR18EZPF2202</t>
+  </si>
+  <si>
+    <t>C2105413</t>
+  </si>
+  <si>
+    <t>R1206</t>
+  </si>
+  <si>
+    <t>R11, R84</t>
+  </si>
+  <si>
+    <t>CRCW04021R00FKEDC</t>
+  </si>
+  <si>
+    <t>C2077765</t>
+  </si>
+  <si>
+    <t>R12A, R12B, R13A, R13B</t>
+  </si>
+  <si>
+    <t>0402WGF5101TCE</t>
+  </si>
+  <si>
+    <t>C25905</t>
+  </si>
+  <si>
+    <t>R20</t>
+  </si>
+  <si>
+    <t>AR05FTC1000</t>
+  </si>
+  <si>
+    <t>C234699</t>
+  </si>
+  <si>
+    <t>R0805</t>
+  </si>
+  <si>
+    <t>R30, R51, R56, R61, R62, R63, R64, R65, R74A, R74B, R74C, R74D, R75A, R75B, R75C, R75D, R77, R83, R95, R98</t>
+  </si>
+  <si>
+    <t>0402WGF1002TCE</t>
+  </si>
+  <si>
+    <t>C25744</t>
+  </si>
+  <si>
+    <t>R42, R85</t>
+  </si>
+  <si>
+    <t>0402WGF3300TCE</t>
+  </si>
+  <si>
+    <t>C25104</t>
+  </si>
+  <si>
+    <t>R48</t>
+  </si>
+  <si>
+    <t>0402WGF7322TCE</t>
+  </si>
+  <si>
+    <t>C26986</t>
+  </si>
+  <si>
+    <t>R49</t>
+  </si>
+  <si>
+    <t>HP05W3F220KT5E</t>
+  </si>
+  <si>
+    <t>C2759317</t>
+  </si>
+  <si>
+    <t>R50</t>
+  </si>
+  <si>
+    <t>0402WGF8872TCE</t>
+  </si>
+  <si>
+    <t>C25922</t>
+  </si>
+  <si>
+    <t>R52, R54</t>
+  </si>
+  <si>
+    <t>0402WGF1501TCE</t>
+  </si>
+  <si>
+    <t>C25867</t>
+  </si>
+  <si>
+    <t>R57, R76</t>
+  </si>
+  <si>
+    <t>0402WGF1003TCE</t>
+  </si>
+  <si>
+    <t>C25741</t>
+  </si>
+  <si>
+    <t>R58</t>
+  </si>
+  <si>
+    <t>0402WGF3302TCE</t>
+  </si>
+  <si>
+    <t>C25779</t>
+  </si>
+  <si>
+    <t>R59</t>
+  </si>
+  <si>
+    <t>FRC0402F4532TS</t>
+  </si>
+  <si>
+    <t>C2933099</t>
+  </si>
+  <si>
+    <t>R66A, R66B, R66C, R66D, R66E, R66F, R66G, R66H, R66I, R66J, R66K, R66L, R66M, R66N, R66O, R66P</t>
+  </si>
+  <si>
+    <t>HP06W2F120KT5E</t>
+  </si>
+  <si>
+    <t>C414958</t>
+  </si>
+  <si>
+    <t>R67A, R67B, R67C, R67D, R67E, R67F, R67G, R67H, R67I, R67J, R67K, R67L, R67M, R67N, R67O, R67P</t>
+  </si>
+  <si>
+    <t>0402WGF6491TCE</t>
+  </si>
+  <si>
+    <t>C25916</t>
+  </si>
+  <si>
+    <t>R68A, R68B, R68C, R68D, R68E, R68F, R68G, R68H, R68I, R68J, R68K, R68L, R68M, R68N, R68O, R68P</t>
+  </si>
+  <si>
+    <t>RC0402FR-076K98L</t>
+  </si>
+  <si>
+    <t>C137944</t>
+  </si>
+  <si>
+    <t>R70A, R70B, R70C, R70D, R71A, R71B, R71C, R71D, R72A, R72B, R72C, R72D, R73A, R73B, R73C, R73D</t>
+  </si>
+  <si>
+    <t>0402WGF0000TCE</t>
+  </si>
+  <si>
+    <t>C17168</t>
+  </si>
+  <si>
+    <t>R79, R80</t>
+  </si>
+  <si>
+    <t>0402WGF6041TCE</t>
+  </si>
+  <si>
+    <t>C25913</t>
+  </si>
+  <si>
+    <t>R86</t>
+  </si>
+  <si>
+    <t>RC0402FR-0712K1L</t>
+  </si>
+  <si>
+    <t>C132157</t>
+  </si>
+  <si>
+    <t>R87, R88, R89, R90</t>
+  </si>
+  <si>
+    <t>0402WGF499JTCE</t>
+  </si>
+  <si>
+    <t>C25120</t>
+  </si>
+  <si>
+    <t>S2, S3</t>
+  </si>
+  <si>
+    <t>TS-1092S-B3D2-G</t>
+  </si>
+  <si>
+    <t>C520860</t>
+  </si>
+  <si>
+    <t>SWITCH_TS-1092S-B3D2-G</t>
+  </si>
+  <si>
+    <t>T1A, T1B, T1C, T1D, T1E, T1F, T1G, T1H, T1I, T1J, T1K, T1L, T1M, T1N, T1O, T1P</t>
+  </si>
+  <si>
+    <t>PH9585.003NLT</t>
+  </si>
+  <si>
+    <t>C17554365</t>
+  </si>
+  <si>
+    <t>PULSE_PH9585</t>
+  </si>
+  <si>
+    <t>TP1, TP2</t>
+  </si>
+  <si>
+    <t>RH-5002</t>
+  </si>
+  <si>
+    <t>C5199802</t>
+  </si>
+  <si>
+    <t>TP_RH-5002</t>
+  </si>
+  <si>
+    <t>TP3, TP4, TP6, TP8, TP10, TP12, TP14, TP16, TP18, TP20, TP22, TP24, TP26, TP28, TP30, TP32, TP33, TP35, TP36, TP37</t>
+  </si>
+  <si>
+    <t>RH-5000</t>
+  </si>
+  <si>
+    <t>C5277086</t>
+  </si>
+  <si>
+    <t>TP_RH-5000</t>
+  </si>
+  <si>
+    <t>TP5, TP7, TP9, TP11, TP13, TP15, TP17, TP19, TP21, TP23, TP25, TP27, TP29, TP31, TP34, TP38, TP39, TP41, TP43, TP45</t>
+  </si>
+  <si>
+    <t>RH-5001</t>
+  </si>
+  <si>
+    <t>C5199801</t>
+  </si>
+  <si>
+    <t>TP_RH-5001</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>STM32F427VGT6</t>
+  </si>
+  <si>
+    <t>C117815</t>
+  </si>
+  <si>
+    <t>100TQFP14</t>
+  </si>
+  <si>
+    <t>U2</t>
+  </si>
+  <si>
+    <t>TPS65263QRHBRQ1</t>
+  </si>
+  <si>
+    <t>C2073290</t>
+  </si>
+  <si>
+    <t>TI_RHB</t>
+  </si>
+  <si>
+    <t>U3A, U3B, U3C, U3D, U3E, U3F, U3G, U3H, U3I, U3J, U3K, U3L, U3M, U3N, U3O, U3P</t>
+  </si>
+  <si>
+    <t>GP82410</t>
+  </si>
+  <si>
+    <t>5SOT23</t>
+  </si>
+  <si>
+    <t>U5A, U5B, U5C, U5D</t>
+  </si>
+  <si>
+    <t>DAC43204RTER</t>
+  </si>
+  <si>
+    <t>16QFN4</t>
+  </si>
+  <si>
+    <t>U6</t>
+  </si>
+  <si>
+    <t>HUSB238A-BB001-QN16R</t>
+  </si>
+  <si>
+    <t>C24833806</t>
+  </si>
+  <si>
+    <t>QFN50P300X300X90-16N</t>
+  </si>
+  <si>
+    <t>U7</t>
+  </si>
+  <si>
+    <t>LAN8742AI-CZ-TR</t>
+  </si>
+  <si>
+    <t>C153279</t>
+  </si>
+  <si>
+    <t>24QFN4E</t>
+  </si>
+  <si>
+    <t>X1, X3</t>
+  </si>
+  <si>
+    <t>XRCGB25M000F3A00R0</t>
+  </si>
+  <si>
+    <t>C467842</t>
+  </si>
+  <si>
+    <t>4_SMD_2.0X1.6MM</t>
+  </si>
+  <si>
+    <t>Comment</t>
+  </si>
+  <si>
+    <t>C5215475</t>
+  </si>
+  <si>
+    <t>C19626938</t>
+  </si>
+  <si>
+    <t>JLCPCB Part #</t>
+  </si>
+  <si>
+    <t>XL-3528RGBW-HM</t>
+  </si>
+  <si>
+    <t>C2843813</t>
+  </si>
+  <si>
+    <t>LED_RGB_SMD3528-4P</t>
+  </si>
+  <si>
     <t>D1</t>
-  </si>
-  <si>
-    <t>ASMB-LTC2-0A335</t>
-  </si>
-  <si>
-    <t>C6466377</t>
-  </si>
-  <si>
-    <t>LED_RGB_ASMB-LTC2-0A335</t>
-  </si>
-  <si>
-    <t>D2, D4A, D4B, D4C, D4D, D4E, D4F, D4G, D4H, D4I, D4J, D4K, D4L, D4M, D4N, D4O, D4P, D7A, D7B, D7C, D7D, D7E, D7F, D7G, D7H, D7I, D7J, D7K, D7L, D7M, D7N, D7O, D7P</t>
-  </si>
-  <si>
-    <t>B340A-13-F</t>
-  </si>
-  <si>
-    <t>C85098</t>
-  </si>
-  <si>
-    <t>SMA</t>
-  </si>
-  <si>
-    <t>D3A, D3B, D3C, D3D, D3E, D3F, D3G, D3H, D3I, D3J, D3K, D3L, D3M, D3N, D3O, D3P</t>
-  </si>
-  <si>
-    <t>PMEG10010ELR-QX</t>
-  </si>
-  <si>
-    <t>C5361358</t>
-  </si>
-  <si>
-    <t>SOD123W</t>
-  </si>
-  <si>
-    <t>D6</t>
-  </si>
-  <si>
-    <t>LTST-C190YKT</t>
-  </si>
-  <si>
-    <t>C125097</t>
-  </si>
-  <si>
-    <t>LED_0603P_YELLOW</t>
-  </si>
-  <si>
-    <t>D9</t>
-  </si>
-  <si>
-    <t>MM3Z15VC</t>
-  </si>
-  <si>
-    <t>C891582</t>
-  </si>
-  <si>
-    <t>SOD323</t>
-  </si>
-  <si>
-    <t>D17A, D17B</t>
-  </si>
-  <si>
-    <t>PESD2USB3UX</t>
-  </si>
-  <si>
-    <t>C3708426</t>
-  </si>
-  <si>
-    <t>3SOT23</t>
-  </si>
-  <si>
-    <t>FB1, FB3</t>
-  </si>
-  <si>
-    <t>BLM15PX601SN1D</t>
-  </si>
-  <si>
-    <t>C160977</t>
-  </si>
-  <si>
-    <t>FB0402</t>
-  </si>
-  <si>
-    <t>FB2</t>
-  </si>
-  <si>
-    <t>MPZ2012S102AT000</t>
-  </si>
-  <si>
-    <t>C76817</t>
-  </si>
-  <si>
-    <t>FB0805</t>
-  </si>
-  <si>
-    <t>H1, H2, H3, H4, H5, H6, H7, H8, H9, H10, H11, H12, H13, H14, H15, H16, H17, H18, H19, H20, H21, H22, H23, H24, H25, H26, H27, H28, H29, H30, H31, H32</t>
-  </si>
-  <si>
-    <t>SMTSO-M2-10ET</t>
-  </si>
-  <si>
-    <t>C2928171</t>
-  </si>
-  <si>
-    <t>J1</t>
-  </si>
-  <si>
-    <t>FTSH-107-01-L-DV-K-A</t>
-  </si>
-  <si>
-    <t>C5563894</t>
-  </si>
-  <si>
-    <t>SAMTEC_FTSH-107-01-L-DV-K-A</t>
-  </si>
-  <si>
-    <t>J2</t>
-  </si>
-  <si>
-    <t>0826-1L1T-57-F</t>
-  </si>
-  <si>
-    <t>C3179913</t>
-  </si>
-  <si>
-    <t>BELFUSE_0826-1L1T-57-F</t>
-  </si>
-  <si>
-    <t>J11A, J11B</t>
-  </si>
-  <si>
-    <t>TYPE-C-31-M-12</t>
-  </si>
-  <si>
-    <t>C165948</t>
-  </si>
-  <si>
-    <t>CONN_USBC_TYPE-C-31-M-12</t>
-  </si>
-  <si>
-    <t>L1, L2, L3</t>
-  </si>
-  <si>
-    <t>FTC404020S4R7MGCA</t>
-  </si>
-  <si>
-    <t>C39676072</t>
-  </si>
-  <si>
-    <t>SMD-4.1x4.1x2.0</t>
-  </si>
-  <si>
-    <t>Q1A, Q1B, Q1C, Q1D, Q1E, Q1F, Q1G, Q1H, Q1I, Q1J, Q1K, Q1L, Q1M, Q1N, Q1O, Q1P</t>
-  </si>
-  <si>
-    <t>IRLML0060TRPBF</t>
-  </si>
-  <si>
-    <t>C67274</t>
-  </si>
-  <si>
-    <t>Q3</t>
-  </si>
-  <si>
-    <t>DMP6023LFGQ-13</t>
-  </si>
-  <si>
-    <t>C672173</t>
-  </si>
-  <si>
-    <t>DIODES_POWERDI3333-8</t>
-  </si>
-  <si>
-    <t>R1, R2, R7, R24, R39, R60, R96, R97</t>
-  </si>
-  <si>
-    <t>0402WGF1001TCE</t>
-  </si>
-  <si>
-    <t>C11702</t>
-  </si>
-  <si>
-    <t>R0402</t>
-  </si>
-  <si>
-    <t>R3, R4, R5, R6, R22, R26, R32, R35, R36, R38, R40, R41, R69A, R69B, R69C, R69D, R81, R82, R91, R92, R93, R128A, R128B, R129A, R129B</t>
-  </si>
-  <si>
-    <t>CRCW040233R0FKED</t>
-  </si>
-  <si>
-    <t>C242490</t>
-  </si>
-  <si>
-    <t>R8A, R8B, R8C, R8D, R8E, R8F, R8G, R8H, R8I, R8J, R8K, R8L, R8M, R8N, R8O, R8P, R14A, R14B, R14C, R14D, R14E, R14F, R14G, R14H, R14I, R14J, R14K, R14L, R14M, R14N, R14O, R14P</t>
-  </si>
-  <si>
-    <t>CRCW06034R70FKEAHP</t>
-  </si>
-  <si>
-    <t>C313771</t>
-  </si>
-  <si>
-    <t>R0603</t>
-  </si>
-  <si>
-    <t>R9, R78</t>
-  </si>
-  <si>
-    <t>0402WGF9103TCE</t>
-  </si>
-  <si>
-    <t>C25800</t>
-  </si>
-  <si>
-    <t>R10A, R10B, R10C, R10D, R10E, R10F, R10G, R10H, R10I, R10J, R10K, R10L, R10M, R10N, R10O, R10P</t>
-  </si>
-  <si>
-    <t>ESR18EZPF2202</t>
-  </si>
-  <si>
-    <t>C2105413</t>
-  </si>
-  <si>
-    <t>R1206</t>
-  </si>
-  <si>
-    <t>R11, R84</t>
-  </si>
-  <si>
-    <t>CRCW04021R00FKEDC</t>
-  </si>
-  <si>
-    <t>C2077765</t>
-  </si>
-  <si>
-    <t>R12A, R12B, R13A, R13B</t>
-  </si>
-  <si>
-    <t>0402WGF5101TCE</t>
-  </si>
-  <si>
-    <t>C25905</t>
-  </si>
-  <si>
-    <t>R20</t>
-  </si>
-  <si>
-    <t>AR05FTC1000</t>
-  </si>
-  <si>
-    <t>C234699</t>
-  </si>
-  <si>
-    <t>R0805</t>
-  </si>
-  <si>
-    <t>R30, R51, R56, R61, R62, R63, R64, R65, R74A, R74B, R74C, R74D, R75A, R75B, R75C, R75D, R77, R83, R95, R98</t>
-  </si>
-  <si>
-    <t>0402WGF1002TCE</t>
-  </si>
-  <si>
-    <t>C25744</t>
-  </si>
-  <si>
-    <t>R42, R85</t>
-  </si>
-  <si>
-    <t>0402WGF3300TCE</t>
-  </si>
-  <si>
-    <t>C25104</t>
-  </si>
-  <si>
-    <t>R48</t>
-  </si>
-  <si>
-    <t>0402WGF7322TCE</t>
-  </si>
-  <si>
-    <t>C26986</t>
-  </si>
-  <si>
-    <t>R49</t>
-  </si>
-  <si>
-    <t>HP05W3F220KT5E</t>
-  </si>
-  <si>
-    <t>C2759317</t>
-  </si>
-  <si>
-    <t>R50</t>
-  </si>
-  <si>
-    <t>0402WGF8872TCE</t>
-  </si>
-  <si>
-    <t>C25922</t>
-  </si>
-  <si>
-    <t>R52, R54</t>
-  </si>
-  <si>
-    <t>0402WGF1501TCE</t>
-  </si>
-  <si>
-    <t>C25867</t>
-  </si>
-  <si>
-    <t>R57, R76</t>
-  </si>
-  <si>
-    <t>0402WGF1003TCE</t>
-  </si>
-  <si>
-    <t>C25741</t>
-  </si>
-  <si>
-    <t>R58</t>
-  </si>
-  <si>
-    <t>0402WGF3302TCE</t>
-  </si>
-  <si>
-    <t>C25779</t>
-  </si>
-  <si>
-    <t>R59</t>
-  </si>
-  <si>
-    <t>FRC0402F4532TS</t>
-  </si>
-  <si>
-    <t>C2933099</t>
-  </si>
-  <si>
-    <t>R66A, R66B, R66C, R66D, R66E, R66F, R66G, R66H, R66I, R66J, R66K, R66L, R66M, R66N, R66O, R66P</t>
-  </si>
-  <si>
-    <t>HP06W2F120KT5E</t>
-  </si>
-  <si>
-    <t>C414958</t>
-  </si>
-  <si>
-    <t>R67A, R67B, R67C, R67D, R67E, R67F, R67G, R67H, R67I, R67J, R67K, R67L, R67M, R67N, R67O, R67P</t>
-  </si>
-  <si>
-    <t>0402WGF6491TCE</t>
-  </si>
-  <si>
-    <t>C25916</t>
-  </si>
-  <si>
-    <t>R68A, R68B, R68C, R68D, R68E, R68F, R68G, R68H, R68I, R68J, R68K, R68L, R68M, R68N, R68O, R68P</t>
-  </si>
-  <si>
-    <t>RC0402FR-076K98L</t>
-  </si>
-  <si>
-    <t>C137944</t>
-  </si>
-  <si>
-    <t>R70A, R70B, R70C, R70D, R71A, R71B, R71C, R71D, R72A, R72B, R72C, R72D, R73A, R73B, R73C, R73D</t>
-  </si>
-  <si>
-    <t>0402WGF0000TCE</t>
-  </si>
-  <si>
-    <t>C17168</t>
-  </si>
-  <si>
-    <t>R79, R80</t>
-  </si>
-  <si>
-    <t>0402WGF6041TCE</t>
-  </si>
-  <si>
-    <t>C25913</t>
-  </si>
-  <si>
-    <t>R86</t>
-  </si>
-  <si>
-    <t>RC0402FR-0712K1L</t>
-  </si>
-  <si>
-    <t>C132157</t>
-  </si>
-  <si>
-    <t>R87, R88, R89, R90</t>
-  </si>
-  <si>
-    <t>0402WGF499JTCE</t>
-  </si>
-  <si>
-    <t>C25120</t>
-  </si>
-  <si>
-    <t>S2, S3</t>
-  </si>
-  <si>
-    <t>TS-1092S-B3D2-G</t>
-  </si>
-  <si>
-    <t>C520860</t>
-  </si>
-  <si>
-    <t>SWITCH_TS-1092S-B3D2-G</t>
-  </si>
-  <si>
-    <t>T1A, T1B, T1C, T1D, T1E, T1F, T1G, T1H, T1I, T1J, T1K, T1L, T1M, T1N, T1O, T1P</t>
-  </si>
-  <si>
-    <t>PH9585.003NLT</t>
-  </si>
-  <si>
-    <t>C17554365</t>
-  </si>
-  <si>
-    <t>PULSE_PH9585</t>
-  </si>
-  <si>
-    <t>TP1, TP2</t>
-  </si>
-  <si>
-    <t>RH-5002</t>
-  </si>
-  <si>
-    <t>C5199802</t>
-  </si>
-  <si>
-    <t>TP_RH-5002</t>
-  </si>
-  <si>
-    <t>TP3, TP4, TP6, TP8, TP10, TP12, TP14, TP16, TP18, TP20, TP22, TP24, TP26, TP28, TP30, TP32, TP33, TP35, TP36, TP37</t>
-  </si>
-  <si>
-    <t>RH-5000</t>
-  </si>
-  <si>
-    <t>C5277086</t>
-  </si>
-  <si>
-    <t>TP_RH-5000</t>
-  </si>
-  <si>
-    <t>TP5, TP7, TP9, TP11, TP13, TP15, TP17, TP19, TP21, TP23, TP25, TP27, TP29, TP31, TP34, TP38, TP39, TP41, TP43, TP45</t>
-  </si>
-  <si>
-    <t>RH-5001</t>
-  </si>
-  <si>
-    <t>C5199801</t>
-  </si>
-  <si>
-    <t>TP_RH-5001</t>
-  </si>
-  <si>
-    <t>U1</t>
-  </si>
-  <si>
-    <t>STM32F427VGT6</t>
-  </si>
-  <si>
-    <t>C117815</t>
-  </si>
-  <si>
-    <t>100TQFP14</t>
-  </si>
-  <si>
-    <t>U2</t>
-  </si>
-  <si>
-    <t>TPS65263QRHBRQ1</t>
-  </si>
-  <si>
-    <t>C2073290</t>
-  </si>
-  <si>
-    <t>TI_RHB</t>
-  </si>
-  <si>
-    <t>U3A, U3B, U3C, U3D, U3E, U3F, U3G, U3H, U3I, U3J, U3K, U3L, U3M, U3N, U3O, U3P</t>
-  </si>
-  <si>
-    <t>GP82410</t>
-  </si>
-  <si>
-    <t>5SOT23</t>
-  </si>
-  <si>
-    <t>U5A, U5B, U5C, U5D</t>
-  </si>
-  <si>
-    <t>DAC43204RTER</t>
-  </si>
-  <si>
-    <t>16QFN4</t>
-  </si>
-  <si>
-    <t>U6</t>
-  </si>
-  <si>
-    <t>HUSB238A-BB001-QN16R</t>
-  </si>
-  <si>
-    <t>C24833806</t>
-  </si>
-  <si>
-    <t>QFN50P300X300X90-16N</t>
-  </si>
-  <si>
-    <t>U7</t>
-  </si>
-  <si>
-    <t>LAN8742AI-CZ-TR</t>
-  </si>
-  <si>
-    <t>C153279</t>
-  </si>
-  <si>
-    <t>24QFN4E</t>
-  </si>
-  <si>
-    <t>X1, X3</t>
-  </si>
-  <si>
-    <t>XRCGB25M000F3A00R0</t>
-  </si>
-  <si>
-    <t>C467842</t>
-  </si>
-  <si>
-    <t>4_SMD_2.0X1.6MM</t>
-  </si>
-  <si>
-    <t>Comment</t>
-  </si>
-  <si>
-    <t>C5215475</t>
-  </si>
-  <si>
-    <t>C19626938</t>
-  </si>
-  <si>
-    <t>JLCPCB Part #</t>
   </si>
 </sst>
 </file>
@@ -1146,7 +1146,7 @@
   <sheetData>
     <row r="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -1155,7 +1155,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
@@ -1384,716 +1384,716 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>58</v>
+        <v>237</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>57</v>
+        <v>240</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>60</v>
+        <v>239</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>59</v>
+        <v>238</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>
